--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:37</t>
+    <t xml:space="preserve">2026-09-09 22:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:22</t>
+    <t xml:space="preserve">2026-09-12 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:39</t>
+    <t xml:space="preserve">2026-09-24 00:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:16</t>
+    <t xml:space="preserve">2026-09-27 22:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:06</t>
+    <t xml:space="preserve">2026-09-29 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -592,7 +592,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>35.65</v>
+        <v>356.51</v>
       </c>
     </row>
     <row r="3">
@@ -609,7 +609,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>29.29</v>
+        <v>292.86</v>
       </c>
     </row>
     <row r="4">
@@ -626,7 +626,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>26.98</v>
+        <v>269.8</v>
       </c>
     </row>
     <row r="5">
@@ -643,7 +643,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>26.66</v>
+        <v>266.61</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>26.47</v>
+        <v>264.7</v>
       </c>
     </row>
     <row r="7">
@@ -677,7 +677,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>26.2</v>
+        <v>262.04</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>25.9</v>
+        <v>259.02</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>24.81</v>
+        <v>248.12</v>
       </c>
     </row>
     <row r="10">
@@ -728,7 +728,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>24.53</v>
+        <v>245.27</v>
       </c>
     </row>
     <row r="11">
@@ -745,7 +745,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>24.27</v>
+        <v>242.71</v>
       </c>
     </row>
     <row r="12">
@@ -762,7 +762,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>23.87</v>
+        <v>238.74</v>
       </c>
     </row>
     <row r="13">
@@ -779,7 +779,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>23.22</v>
+        <v>232.19</v>
       </c>
     </row>
     <row r="14">
@@ -796,7 +796,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>23.07</v>
+        <v>230.66</v>
       </c>
     </row>
     <row r="15">
@@ -813,7 +813,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>22.44</v>
+        <v>224.38</v>
       </c>
     </row>
     <row r="16">
@@ -830,7 +830,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>21.81</v>
+        <v>218.12</v>
       </c>
     </row>
     <row r="17">
@@ -847,7 +847,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>21.76</v>
+        <v>217.59</v>
       </c>
     </row>
     <row r="18">
@@ -864,7 +864,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>21.62</v>
+        <v>216.24</v>
       </c>
     </row>
     <row r="19">
@@ -881,7 +881,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>20.52</v>
+        <v>205.2</v>
       </c>
     </row>
     <row r="20">
@@ -898,7 +898,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>20.4</v>
+        <v>204.02</v>
       </c>
     </row>
     <row r="21">
@@ -915,7 +915,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>20.26</v>
+        <v>202.63</v>
       </c>
     </row>
     <row r="22">
@@ -932,7 +932,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>19.29</v>
+        <v>192.86</v>
       </c>
     </row>
     <row r="23">
@@ -949,7 +949,7 @@
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>18.81</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="24">
@@ -966,7 +966,7 @@
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>17.85</v>
+        <v>178.51</v>
       </c>
     </row>
     <row r="25">
@@ -983,7 +983,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>16.84</v>
+        <v>168.37</v>
       </c>
     </row>
     <row r="26">
@@ -1000,7 +1000,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>16.18</v>
+        <v>161.84</v>
       </c>
     </row>
     <row r="27">
@@ -1017,7 +1017,7 @@
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>15.51</v>
+        <v>155.1</v>
       </c>
     </row>
     <row r="28">
@@ -1034,7 +1034,7 @@
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>14.87</v>
+        <v>148.69</v>
       </c>
     </row>
     <row r="29">
@@ -1051,7 +1051,7 @@
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>14.78</v>
+        <v>147.83</v>
       </c>
     </row>
     <row r="30">
@@ -1068,7 +1068,7 @@
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>14.53</v>
+        <v>145.28</v>
       </c>
     </row>
     <row r="31">
@@ -1085,7 +1085,7 @@
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>14.34</v>
+        <v>143.44</v>
       </c>
     </row>
     <row r="32">
@@ -1102,7 +1102,7 @@
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>14.26</v>
+        <v>142.59</v>
       </c>
     </row>
     <row r="33">
@@ -1119,7 +1119,7 @@
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>14.05</v>
+        <v>140.46</v>
       </c>
     </row>
     <row r="34">
@@ -1136,7 +1136,7 @@
         <v>2021</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>13.34</v>
+        <v>133.4</v>
       </c>
     </row>
     <row r="35">
@@ -1153,7 +1153,7 @@
         <v>2021</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>12.59</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="36">
@@ -1170,7 +1170,7 @@
         <v>2021</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>12.29</v>
+        <v>122.87</v>
       </c>
     </row>
     <row r="37">
@@ -1187,7 +1187,7 @@
         <v>2021</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>11.5</v>
+        <v>114.99</v>
       </c>
     </row>
     <row r="38">
@@ -1204,7 +1204,7 @@
         <v>2021</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11.47</v>
+        <v>114.71</v>
       </c>
     </row>
     <row r="39">
@@ -1221,7 +1221,7 @@
         <v>2021</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>10.5</v>
+        <v>104.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:00</t>
+    <t xml:space="preserve">2026-10-01 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -174,7 +174,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:25</t>
+    <t xml:space="preserve">2026-10-02 13:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:06</t>
+    <t xml:space="preserve">2026-10-04 07:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:57</t>
+    <t xml:space="preserve">2026-10-05 07:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
